--- a/光伏配储项目/电价数据/2026/钰海电厂.xlsx
+++ b/光伏配储项目/电价数据/2026/钰海电厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55445</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.62575</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.01336</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.16272</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.12339</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.07527</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.9355800000000001</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.94065</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.62962</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.6151599999999999</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.9204600000000001</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.9205800000000001</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.91535</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.60848</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.92989</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.92471</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.90507</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.91861</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.63955</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.9262</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.6373799999999999</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.9251699999999999</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.9312</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.66086</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.9560299999999999</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.04366</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.87575</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.6880700000000001</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.68416</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.46392</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.74988</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.77312</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.03673</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.02194</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.11438</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.7599</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.71697</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.51335</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.41035</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40684</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41037</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7918500000000001</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.97239</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.34069</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.53173</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.77649</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.45151</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.78449</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.76006</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.9133600000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.0691</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.34025</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.16797</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.18602</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.74288</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.23157</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.18613</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10532</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.24662</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.54515</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.18467</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.26994</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.49415</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.32538</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.25366</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.44119</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.37136</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.30207</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.8120599999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47986</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.422</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.18233</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04959</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53767</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52274</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5143300000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.70521</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.60626</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.67948</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.5849800000000001</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.57751</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.65423</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.6180099999999999</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.6233300000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.6233300000000001</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.6179</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.6124299999999999</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.66772</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.92308</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.25598</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.93843</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.68296</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.57825</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.63825</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.54701</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.5748300000000001</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.95037</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.16563</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.7893300000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.13512</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.0516</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.00638</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.71673</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54974</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.57175</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.68613</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.24551</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.49203</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.18606</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.66278</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.08906</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.83327</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.26205</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.15806</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28919</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.6244500000000001</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.63832</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.56587</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.18599</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.18591</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.99336</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.18731</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.18479</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.68066</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.18727</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.21321</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.24359</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.54186</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.44896</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.18723</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.5116</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.27146</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.74714</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7628400000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9205</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.6699700000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.80935</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.7882</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.5863700000000001</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.65785</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.57368</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.76035</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.76087</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.72076</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.65527</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.78067</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.61091</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.75383</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.56308</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.65649</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.58227</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.64647</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.61453</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.6063099999999999</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.6158400000000001</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.6215599999999999</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.55803</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.70182</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8402000000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.11777</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.89936</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.76515</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.72637</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.63976</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.65012</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.43834</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.76024</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.1861</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.55539</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.72558</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.19722</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.65268</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19462</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.18581</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.79811</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.95761</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.18598</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.18595</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.9027200000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.56289</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42086</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67877</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.04394</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.18602</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.4228</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.25799</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.18605</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21859</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21339</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.42663</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.27863</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.29952</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.66758</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.19603</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.19829</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.05869</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.09407</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.11518</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.10117</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.22593</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.18606</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.26971</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.01229</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.76391</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.72051</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53522</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.16144</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.8441000000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.83382</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.77387</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.7946799999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.96536</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.65071</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.73633</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.81663</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.75629</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.7084900000000001</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.62612</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.6223500000000001</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.47547</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.5489400000000001</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.4753</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.50317</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.6315</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.6284400000000001</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.72725</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.61442</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.5874199999999999</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.5483300000000001</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.51911</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.68345</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.7261599999999999</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.93936</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.18596</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.85277</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.57119</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66554</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.9039199999999999</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.88086</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16066</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.4267</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77312</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9709500000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.22979</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.69659</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12242</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.5242</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48738</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.65832</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.00136</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10994</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.25853</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.18576</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.08375</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.00157</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03444</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.99841</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.29271</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.47409</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.81292</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.23118</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.86475</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.10446</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.18493</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.1334</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.28398</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.34477</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.29783</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.2032</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19279</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.21475</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.22589</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.21155</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.73885</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.52887</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7483300000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32174</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74949</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49488</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.48003</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.5102099999999999</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52577</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.46155</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43094</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.46078</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.7226</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.85573</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.61895</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70727</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.73211</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.85573</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.71246</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55384</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.55384</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.59812</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47749</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.10076</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5515099999999999</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.4859</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.51819</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.64866</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.51225</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.49138</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49689</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49716</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.6141599999999999</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.5151699999999999</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.51422</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.4117</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49193</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41076</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34425</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.21257</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.99453</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.00967</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.59865</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.72002</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.66476</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.6230399999999999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.66437</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.6482599999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.6473</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.91977</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.65524</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.65564</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.64654</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.6465299999999999</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.64679</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07482</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.03971</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.26942</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.07823000000000001</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12409</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.00375</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.43028</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.6930599999999999</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.66315</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.6750499999999999</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.66344</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.6632100000000001</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33412</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.65724</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.57112</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27247</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.76489</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.90154</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.6985</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6984900000000001</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.7046399999999999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.76873</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.97888</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.44682</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.49565</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.75683</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.74858</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.9198</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.67045</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.5460900000000001</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48497</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45618</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09348999999999999</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.74891</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.74822</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6487200000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.61097</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48067</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.73919</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7908500000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7904800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6100599999999999</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.02996</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.42964</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.85995</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.4604</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.34811</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.81448</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.4085</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.06444</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.4269</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.79038</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.4666</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7902</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8042699999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78813</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8808400000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50562</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4157</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46409</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22281</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54213</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.7087599999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.6839500000000001</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.67377</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.67832</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.68148</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.6000700000000001</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.6821799999999999</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.67184</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.56099</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.56541</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.57182</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.66218</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.6474800000000001</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.65135</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.6490199999999999</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.66671</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.6494800000000001</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.65739</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.56259</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.72621</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.56541</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60037</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43718</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5644199999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6687799999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07797</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.65549</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.52899</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57624</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59662</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.96499</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33878</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30752</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.28163</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.57064</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8001200000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5774600000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.6559299999999999</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55777</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>1.01314</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.79032</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.73505</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.64362</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5826699999999999</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.01149</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.04897</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.56062</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.7108300000000001</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.66415</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.73473</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.66431</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.71027</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.8053400000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.6978</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.71009</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.6081599999999999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5926399999999999</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.7089299999999999</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.7376900000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.7084900000000001</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.7341799999999999</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.7455700000000001</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.78307</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.73998</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.7863600000000001</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.74494</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.74012</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.74146</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.73549</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.7298600000000001</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.71172</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.7294400000000001</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.66395</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.70325</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.66928</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.68206</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.67004</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.66249</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.6571699999999999</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.56064</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9511799999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.65661</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.76549</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.75258</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.80533</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.6535299999999999</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.65924</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.59266</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.62937</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.5654199999999999</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.6628999999999999</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.53166</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.62874</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.74818</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.89767</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.15061</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.94021</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5596599999999999</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12493</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.8665</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9740599999999999</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8837200000000001</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.65334</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.8366699999999999</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.09538</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.6632100000000001</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.53366</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.89767</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.10487</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.76824</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.23127</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.83729</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.8442999999999999</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.75919</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47784</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44475</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41583</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.20022</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51553</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79415</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6489400000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5828300000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.7323999999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.75917</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.17904</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.92357</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.6579700000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.77179</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.7107899999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.56161</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.60091</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.11369</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61376</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.9040900000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.5981599999999999</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.38213</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.35735</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.32303</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.3222</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.60828</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.9148500000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.53653</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.59526</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.8660599999999999</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.52744</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.75963</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07468</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.09623</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.93153</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.94894</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.18601</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.18456</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.88855</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.18466</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.63091</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.99709</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.04128</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.18461</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.9777</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.01858</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.57946</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.94186</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.00719</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.0626</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.91223</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.89142</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.68461</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.12447</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.61075</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.9865499999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.02341</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.75958</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33728</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.7436900000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.61129</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.61285</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.5981300000000001</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.5171</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.65677</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.7536</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.61134</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.61086</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.58416</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.63046</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.7101499999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.6621900000000001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.9832000000000001</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.19203</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.6622</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.66232</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.6620499999999999</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.60224</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.59234</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.65438</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.74695</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.71096</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.6621900000000001</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.5432899999999999</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.53284</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.5463899999999999</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.55148</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.68998</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.61534</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.59849</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45671</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.5995</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.59739</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.59781</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5764199999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.49561</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.52996</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.72405</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.6544</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.65789</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.65108</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.67399</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.5883400000000001</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.6215000000000001</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.5144099999999999</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.44586</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.5137200000000001</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.44586</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.6266900000000001</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.65604</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.63807</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.5849099999999999</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.5781900000000001</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.54659</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.59293</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.6997599999999999</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6002999999999999</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6267200000000001</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8502999999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.26805</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16556</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8502999999999999</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.4503</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42971</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7000700000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.9502999999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.18399</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.1328</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.13012</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.55004</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42917</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49781</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44691</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42568</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56592</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.55143</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.5492400000000001</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.55143</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.5171399999999999</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.6324299999999999</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.51871</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.57474</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.63502</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.59794</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.67145</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.97365</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.31548</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.21171</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.99993</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.9883200000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9892300000000001</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56068</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55656</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94313</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.10067</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.02011</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.79367</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65846</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64846</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.73717</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.80887</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29232</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.76061</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.35048</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.48392</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.15664</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.98323</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.64846</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.63346</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.66619</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67855</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67363</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.6504</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67346</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.2068</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70859</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78899</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70495</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.7133</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.72071</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.6399</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.01912</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12845</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69966</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70731</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.70169</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.78598</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.73083</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.81992</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.67092</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46513</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.1792</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.5572</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.67144</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.5465599999999999</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.57992</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34416</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.54149</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.69259</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.27634</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.56702</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.63162</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.55074</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.65291</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.63146</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.62878</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.5574600000000001</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.53211</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.75314</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49527</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51344</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.52206</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45336</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92989</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48406</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18929</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.9003</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76634</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39542</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49986</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.4503</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48995</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34925</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.53207</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75318</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.5179</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.70361</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49986</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56631</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42607</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66338</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.44597</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6411</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.81696</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44708</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.6137899999999999</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.5784</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.57336</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.9781599999999999</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.56169</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.50685</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.48001</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.42938</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.44893</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.4387200000000001</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.5160800000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.42003</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5516799999999999</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7605700000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.7661399999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27876</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48294</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54401</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7356</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76059</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5527000000000001</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01768</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48189</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.45533</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.10404</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.13317</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.09153</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.12108</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.13828</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.02722</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.20266</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.15055</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13848</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.19419</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.85096</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19896</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8558300000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.3531</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9007999999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.71269</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75293</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9619099999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.4934</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.63237</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.62207</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.66408</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.53826</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7603300000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.41365</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.56154</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.77955</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.7709</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.62052</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.6026699999999999</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.7219</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.7375499999999999</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.7409</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.61664</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.7485299999999999</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.62283</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.72826</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.57628</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.51944</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.52535</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.52535</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.5761499999999999</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.45382</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.53788</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46321</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.70021</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.58516</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5381</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.78084</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.59821</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.1091</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.79478</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.76012</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.29662</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.35838</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.73688</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.66197</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.36724</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.00317</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.60825</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49985</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49986</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.5993099999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.7507999999999999</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.19984</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.70533</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.93752</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.95917</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.8986000000000001</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.76234</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.73205</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18339</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.18689</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.44862</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.26612</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.67009</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.25162</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.29685</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.1141</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.43813</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.04469</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.8218799999999999</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.77573</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.25573</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.67061</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48696</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.54525</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.46699</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48721</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40568</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5335700000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.79831</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.68325</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.65566</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50426</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.08485</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.69185</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66457</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.8065099999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.0809</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.19341</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19338</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54299</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.1537</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55455</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.56489</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49977</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50003</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.52222</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.51737</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.7603</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.13864</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.7813600000000001</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.65798</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.47301</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.39769</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49957</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44986</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.59414</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48357</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.46242</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46334</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5529700000000001</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46107</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46926</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.59468</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.56767</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.5720700000000001</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.59023</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.5520700000000001</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.41813</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3847</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.95812</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.5898099999999999</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.45165</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.46047</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.53307</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.5271699999999999</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.52207</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.52207</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23376</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.15323</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.7365499999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.21449</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.27288</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.14007</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.69937</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.57526</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49954</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.6289</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.43175</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.42865</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.8079500000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46778</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39311</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.49012</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.10152</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.38349</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.02223</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.94404</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5253099999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7601599999999999</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.7601100000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51497</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44463</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.5578099999999999</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42592</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.01429</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6677000000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.8050499999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.76018</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41107</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52859</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.38192</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.38632</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.24325</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.0877</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.98593</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.6355</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.54971</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49706</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5828</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.76002</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.55067</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5495800000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.7599900000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.7600399999999999</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.58397</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45087</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49807</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.01223</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.77052</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.62771</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.7600399999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.20381</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6085499999999999</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.7507999999999999</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.26729</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.9011699999999999</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.88559</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.90599</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.92444</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.17603</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.6507999999999999</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.9591900000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.69437</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.98505</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.65762</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.67811</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.75879</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.65762</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.26426</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04491</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.02592</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.03481</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.54721</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.3634</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.0573</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.7602300000000001</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34549</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5590900000000001</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80823</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5498200000000001</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7579400000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7602300000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.47037</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45976</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42899</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40319</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42643</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.63675</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59568</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.54299</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45233</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.48114</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49969</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.56036</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.14061</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.0516</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.1531</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.75585</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.7448</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.06003</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.08398</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.68431</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5550499999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47984</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48414</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5500499999999999</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.5460499999999999</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.6616000000000001</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.55556</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.0516</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.6616000000000001</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49983</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49984</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48249</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49985</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49987</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57817</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5577000000000001</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49986</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5140800000000001</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.5016</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.6616000000000001</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.07744</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6616000000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58262</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8716</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6616000000000001</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.16126</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49987</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.51185</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49986</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.44036</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53542</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34476</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.8831100000000001</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.67249</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.68008</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.95725</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.6566000000000001</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41993</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6297699999999999</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58923</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42189</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.64213</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.03851</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.26894</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9355</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.9862799999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.03412</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.9770399999999999</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.9445399999999999</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.97505</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.95802</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.9426599999999999</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9526100000000001</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.44012</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.7895800000000001</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.14246</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.7212000000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.13882</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.22402</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.20549</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.72825</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.94812</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.86833</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.93545</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54956</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.72789</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.75199</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.77524</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.22285</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.09178</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.02956</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.33905</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.02559</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.10358</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.92969</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.76437</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.76244</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.82059</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.70704</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.7000299999999999</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5689</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.69302</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.74127</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6996100000000001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7602300000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40362</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.71001</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46638</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.7497200000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5241699999999999</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.5105299999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.0237</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.9218500000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.03424</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.93224</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.05224</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.03124</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.02924</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.28301</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.09519</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.20849</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.5651900000000001</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.68088</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.6238899999999999</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.7360800000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.72156</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02286</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.72184</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.77325</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.14568</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.33441</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.55214</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.73533</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.32059</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.47651</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.08116</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.51605</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.4748</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.7826</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.54735</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.81423</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.76918</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80872</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.6803400000000001</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.45915</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.7601</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.41882</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49983</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.80949</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31084</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00208</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9270900000000001</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.95408</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03637</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.1654</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.07094</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.8725700000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69086</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.23508</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.21176</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.2144</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15104</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.8659</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70133</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09181</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10245</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10283</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.1299</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10175</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.51738</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.19706</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.6574500000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.57928</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15172</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.7459199999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.67191</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.8699199999999999</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.0683</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.0607</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.09338</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03565</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06691</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.11466</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.0472</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.0591</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16156</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.23667</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.19639</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.29774</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.1682</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.17862</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11799</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09946</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12481</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.1918</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.11324</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.69017</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.62763</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.57589</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.55662</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44926</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37619</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.55204</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31083</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31082</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06579</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48155</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.52022</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.49233</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.46271</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.46111</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.47678</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.49144</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.47842</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.48471</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.47999</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.47796</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.47404</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.47724</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.46982</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.4591</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.45722</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.44789</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84793</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.45628</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.5768099999999999</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.70075</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.71609</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.66706</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.94575</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7594099999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.95886</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.17259</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30844</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.4477</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43693</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.46616</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54823</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.26345</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85029</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.67512</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73245</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.70669</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.51159</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84945</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.91674</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.22247</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.80213</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.5993200000000001</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.64036</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.73621</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.62524</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7385499999999999</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.60795</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.18525</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17917</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41464</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17936</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17518</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.09111</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.0652</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.17959</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.08527</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.04359</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.06856</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.19308</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08331</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54195</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80729</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80336</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56426</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.20021</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84829</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8482799999999999</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55883</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55414</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.5152599999999999</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55344</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41936</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52081</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50081</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45944</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43854</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.4951</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54772</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5208200000000001</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52081</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55706</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8826900000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49289</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17062</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50865</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5701900000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84394</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79488</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59685</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85168</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50322</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5208700000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5445399999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.69947</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.5555599999999999</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.18273</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54926</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5488200000000001</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58117</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.7994</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55457</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.79804</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.84962</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17407</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7993400000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68336</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.04977</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17354</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8219299999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.64479</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6730700000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6804</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7259800000000001</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.82921</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.80852</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6008600000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.7990700000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.74775</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.12918</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.74482</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60082</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.6231599999999999</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.6276</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.60081</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.60081</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.68886</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6500199999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.79965</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.6907000000000001</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.59984</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37241</v>
       </c>
     </row>
   </sheetData>
